--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="228">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T12:52:51+00:00</t>
+    <t>2025-02-24T13:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>Performer1.typeId.nullFlavor</t>
@@ -1588,7 +1584,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1596,10 +1592,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1697,39 +1693,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1780,7 +1776,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1800,39 +1796,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1883,7 +1879,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1903,39 +1899,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1944,49 +1940,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2006,17 +2002,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2034,11 +2030,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2089,7 +2085,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2109,10 +2105,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2139,7 +2135,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2190,7 +2186,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2210,10 +2206,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2239,7 +2235,7 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2271,7 +2267,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2289,7 +2285,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2309,10 +2305,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2335,10 +2331,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2390,7 +2386,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2410,10 +2406,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2436,10 +2432,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2491,7 +2487,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2511,10 +2507,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2537,10 +2533,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2592,7 +2588,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2612,10 +2608,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2713,10 +2709,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2814,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2907,7 +2903,7 @@
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2915,10 +2911,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3016,39 +3012,39 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3099,7 +3095,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3119,39 +3115,39 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3202,7 +3198,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3222,39 +3218,39 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3263,49 +3259,49 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3325,17 +3321,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>75</v>
@@ -3353,11 +3349,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3408,7 +3404,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3428,10 +3424,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3458,7 +3454,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3509,7 +3505,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3529,10 +3525,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3566,7 +3562,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3588,25 +3584,25 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3626,10 +3622,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3655,7 +3651,7 @@
         <v>95</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3707,7 +3703,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3727,10 +3723,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3828,39 +3824,39 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3911,7 +3907,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3931,39 +3927,39 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4014,7 +4010,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4034,41 +4030,41 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="F30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="L30" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4119,7 +4115,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4139,41 +4135,41 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4224,7 +4220,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4244,10 +4240,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4270,7 +4266,7 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -4323,7 +4319,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4343,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4369,10 +4365,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4404,25 +4400,25 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4442,10 +4438,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4543,10 +4539,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4575,7 +4571,7 @@
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4626,7 +4622,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4646,17 +4642,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4674,11 +4670,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4729,7 +4725,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4749,17 +4745,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4777,11 +4773,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4832,7 +4828,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4852,17 +4848,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4880,11 +4876,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4935,7 +4931,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4955,17 +4951,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -4983,11 +4979,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5038,7 +5034,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5058,10 +5054,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5084,11 +5080,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5139,7 +5135,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5159,10 +5155,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5185,11 +5181,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5240,7 +5236,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5260,39 +5256,39 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="F42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5343,7 +5339,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5363,39 +5359,39 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5446,7 +5442,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5466,17 +5462,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5494,11 +5490,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5549,7 +5545,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5569,10 +5565,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5595,10 +5591,10 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -5650,7 +5646,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5670,10 +5666,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5696,10 +5692,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -5751,7 +5747,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5771,10 +5767,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5797,10 +5793,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -5852,7 +5848,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5872,10 +5868,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5898,10 +5894,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -5953,7 +5949,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5973,10 +5969,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5999,7 +5995,7 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6052,7 +6048,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6072,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6151,7 +6147,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>performer</t>
+    <t>CDA - performer</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1033,42 +1033,42 @@
   <dimension ref="A1:AK50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.19140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.80078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.75390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
